--- a/output/pdf_financials_xlsx/BNG.xlsx
+++ b/output/pdf_financials_xlsx/BNG.xlsx
@@ -7793,52 +7793,52 @@
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-3.338</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-10.213</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-16.017</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-1.963</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-3.189</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.761</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.407</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-2.277</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.93</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.022</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.061</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-1.231</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-2.227</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-0.077</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-0.014</v>
       </c>
       <c r="S118" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="119">
@@ -9334,7 +9334,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>-</t>
@@ -31126,7 +31130,11 @@
           <t>Exploration and evaluation expenditures 7</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -39548,7 +39556,11 @@
           <t>Exploration and evaluation expenditures 8</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -41450,7 +41462,11 @@
           <t>Exploration and evaluation expenditures 5</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -43318,7 +43334,11 @@
           <t>Exploration and evaluation expenditures 4</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
           <t>-</t>
@@ -46966,7 +46986,11 @@
           <t>Exploration and evaluation expenditures 6</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -48956,7 +48980,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BNG.xlsx
+++ b/output/pdf_financials_xlsx/BNG.xlsx
@@ -1110,22 +1110,22 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.013</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.018</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>0</v>
@@ -2165,22 +2165,22 @@
         <v>-2.768</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-12.271</v>
+        <v>-12.258</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.475</v>
+        <v>-2.465</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.896</v>
+        <v>-2.892</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>3.928</v>
+        <v>3.929</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.374</v>
+        <v>-0.367</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.703</v>
+        <v>0.721</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>-12.728</v>
@@ -2287,22 +2287,22 @@
         <v>-0.459</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-10.231</v>
+        <v>-10.218</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.018</v>
+        <v>-1.008</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.499</v>
+        <v>-1.495</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>5.261</v>
+        <v>5.262</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.775</v>
+        <v>1.793</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>-11.488</v>
@@ -2360,22 +2360,22 @@
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-101.6189908621375</v>
+        <v>-101.4898688915376</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-9.566770040409736</v>
+        <v>-9.472793910346772</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-19.25003210479003</v>
+        <v>-19.19866444073456</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>106.9308943089431</v>
+        <v>106.9512195121951</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>9.637046307884855</v>
+        <v>9.734390209984703</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>23.50059578975242</v>
+        <v>23.73891169071892</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>-177.2565962042895</v>
@@ -8210,19 +8210,19 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.053</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.036</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.032</v>
       </c>
       <c r="R124" s="3" t="n">
         <v>0</v>
@@ -8275,19 +8275,19 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.053</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.036</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.032</v>
       </c>
       <c r="R125" s="3" t="n">
         <v>0</v>
@@ -32676,7 +32676,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -36930,7 +36934,11 @@
           <t>Lease payments 12</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -40298,7 +40306,11 @@
           <t>Lease payments 13</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -58728,7 +58740,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -62380,7 +62392,7 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">

--- a/output/pdf_financials_xlsx/BNG.xlsx
+++ b/output/pdf_financials_xlsx/BNG.xlsx
@@ -7953,10 +7953,10 @@
         <v>0</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>0</v>
+        <v>16.536</v>
       </c>
       <c r="O120" s="3" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="P120" s="3" t="n">
         <v>0</v>
@@ -35364,7 +35364,11 @@
           <t>Issuance of common shares, net of issuance costs 12</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -36830,7 +36834,11 @@
           <t>Issuance of common shares, net of issuance costs 14</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BNG.xlsx
+++ b/output/pdf_financials_xlsx/BNG.xlsx
@@ -1400,10 +1400,10 @@
         <v>-0</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.008</v>
+        <v>-0.008</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.055</v>
+        <v>-0.055</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0</v>
@@ -2928,31 +2928,31 @@
         <v>0</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.093</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="41">
@@ -2989,31 +2989,31 @@
         <v>3.575</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>4.307</v>
+        <v>4.4</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>2.972</v>
+        <v>3.016</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>1.639</v>
+        <v>1.65</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>1.224</v>
+        <v>1.242</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>2.646</v>
+        <v>2.657</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>1.085</v>
+        <v>1.094</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>1.782</v>
+        <v>1.789</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>1.682</v>
+        <v>1.688</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>2.214</v>
+        <v>2.218</v>
       </c>
     </row>
     <row r="42">
@@ -3416,31 +3416,31 @@
         <v>1.153</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.294</v>
+        <v>0.201</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.453</v>
+        <v>0.409</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.713</v>
+        <v>1.702</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.485</v>
+        <v>0.467</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.658</v>
+        <v>0.647</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.903</v>
+        <v>0.894</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.903</v>
+        <v>0.896</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.98</v>
+        <v>0.974</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.893</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="49">
@@ -4627,25 +4627,25 @@
         <v>0</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>1.049</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.624</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.505</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.841</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.646</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.599</v>
       </c>
       <c r="R67" s="3" t="n">
         <v>0</v>
@@ -4691,22 +4691,22 @@
         <v>2.232</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>2.574</v>
+        <v>3.623</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>1.041</v>
+        <v>1.665</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>1.939</v>
+        <v>2.444</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>3.211</v>
+        <v>4.052</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>3.035</v>
+        <v>3.681</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>3.178</v>
+        <v>3.777</v>
       </c>
       <c r="R68" s="3" t="n">
         <v>1.794</v>
@@ -5121,16 +5121,16 @@
         <v>0</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.032</v>
+        <v>0</v>
       </c>
       <c r="Q75" s="3" t="n">
         <v>0</v>
@@ -46580,7 +46580,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>
@@ -48476,7 +48480,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
           <t>-</t>
@@ -73254,7 +73262,11 @@
           <t>Deferred income tax recovery 9</t>
         </is>
       </c>
-      <c r="D620" t="inlineStr"/>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E620" t="inlineStr">
         <is>
           <t>-</t>
@@ -74516,7 +74528,11 @@
           <t>Deferred income tax recovery 10</t>
         </is>
       </c>
-      <c r="D632" t="inlineStr"/>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E632" t="inlineStr">
         <is>
           <t>-</t>
